--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488241_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488241_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. PAREDES BERMEJO</t>
+          <t>P. OSES BERNALDEZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.6202</v>
+        <v>8.299899999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>4.8131</v>
+        <v>5.3177</v>
       </c>
       <c r="F2" t="n">
-        <v>2.8071</v>
+        <v>2.9822</v>
       </c>
       <c r="G2" t="n">
-        <v>8.1114</v>
+        <v>3.6254</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.6267</v>
+        <v>0.1787</v>
       </c>
       <c r="I2" t="n">
-        <v>8.738099999999999</v>
+        <v>3.4466</v>
       </c>
       <c r="J2" t="n">
-        <v>6.7791</v>
+        <v>3.3694</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.4381</v>
+        <v>0.5066000000000001</v>
       </c>
       <c r="L2" t="n">
-        <v>7.2173</v>
+        <v>2.8628</v>
       </c>
       <c r="M2" t="n">
-        <v>1.3323</v>
+        <v>0.256</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.1885</v>
+        <v>-0.3278</v>
       </c>
       <c r="O2" t="n">
-        <v>1.5209</v>
+        <v>0.5839</v>
       </c>
       <c r="P2" t="n">
-        <v>0.5558999999999999</v>
+        <v>1.6676</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.4823</v>
+        <v>1.6676</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.7327</v>
+        <v>0.8043</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.0396</v>
+        <v>0.0606</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3069</v>
+        <v>0.7436</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.3144</v>
+        <v>2.2027</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.8877</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.3144</v>
+        <v>0.315</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>P. OSES BERNALDEZ</t>
+          <t>J. PAREDES BERMEJO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.394</v>
+        <v>8.1831</v>
       </c>
       <c r="E3" t="n">
-        <v>4.4364</v>
+        <v>5.4007</v>
       </c>
       <c r="F3" t="n">
-        <v>2.9576</v>
+        <v>2.7824</v>
       </c>
       <c r="G3" t="n">
-        <v>3.6254</v>
+        <v>8.1114</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1787</v>
+        <v>-0.6267</v>
       </c>
       <c r="I3" t="n">
-        <v>3.4466</v>
+        <v>8.738099999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>3.3694</v>
+        <v>6.7791</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5066000000000001</v>
+        <v>-0.4381</v>
       </c>
       <c r="L3" t="n">
-        <v>2.8628</v>
+        <v>7.2173</v>
       </c>
       <c r="M3" t="n">
-        <v>0.256</v>
+        <v>1.3323</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.3278</v>
+        <v>-0.1885</v>
       </c>
       <c r="O3" t="n">
-        <v>0.5839</v>
+        <v>1.5209</v>
       </c>
       <c r="P3" t="n">
-        <v>1.6676</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R3" t="n">
-        <v>1.6676</v>
+        <v>1.4823</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1017</v>
+        <v>-0.1697</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8207</v>
+        <v>-0.452</v>
       </c>
       <c r="U3" t="n">
-        <v>0.719</v>
+        <v>0.2823</v>
       </c>
       <c r="V3" t="n">
-        <v>2.2027</v>
+        <v>-0.3144</v>
       </c>
       <c r="W3" t="n">
-        <v>1.8877</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0.315</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R. ALOGO EVUNA</t>
+          <t>A. MEJIA BERIGUETE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>6.6796</v>
+        <v>5.4421</v>
       </c>
       <c r="E4" t="n">
-        <v>2.507</v>
+        <v>3.4285</v>
       </c>
       <c r="F4" t="n">
-        <v>4.1726</v>
+        <v>2.0135</v>
       </c>
       <c r="G4" t="n">
-        <v>2.0997</v>
+        <v>4.9903</v>
       </c>
       <c r="H4" t="n">
-        <v>-3.4361</v>
+        <v>0.5652</v>
       </c>
       <c r="I4" t="n">
-        <v>5.5358</v>
+        <v>4.4251</v>
       </c>
       <c r="J4" t="n">
-        <v>2.4327</v>
+        <v>4.4355</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.7358</v>
+        <v>0.4636</v>
       </c>
       <c r="L4" t="n">
-        <v>4.1685</v>
+        <v>3.9718</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.333</v>
+        <v>0.5548999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.7003</v>
+        <v>0.1016</v>
       </c>
       <c r="O4" t="n">
-        <v>1.3673</v>
+        <v>0.4533</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3706</v>
+        <v>0.1853</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.8529</v>
+        <v>-0.9264</v>
       </c>
       <c r="R4" t="n">
-        <v>2.2234</v>
+        <v>1.1117</v>
       </c>
       <c r="S4" t="n">
-        <v>2.9504</v>
+        <v>0.2664</v>
       </c>
       <c r="T4" t="n">
-        <v>1.2983</v>
+        <v>-0.0805</v>
       </c>
       <c r="U4" t="n">
-        <v>1.6521</v>
+        <v>0.3469</v>
       </c>
       <c r="V4" t="n">
-        <v>1.2589</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.6289</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0.63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. DIAZ FERREIRA</t>
+          <t>R. ALOGO EVUNA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>5.7876</v>
+        <v>4.9375</v>
       </c>
       <c r="E5" t="n">
-        <v>2.3994</v>
+        <v>1.4298</v>
       </c>
       <c r="F5" t="n">
-        <v>3.3882</v>
+        <v>3.5078</v>
       </c>
       <c r="G5" t="n">
-        <v>1.7277</v>
+        <v>2.0997</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1126</v>
+        <v>-3.4361</v>
       </c>
       <c r="I5" t="n">
-        <v>1.8403</v>
+        <v>5.5358</v>
       </c>
       <c r="J5" t="n">
-        <v>1.463</v>
+        <v>2.4327</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4677</v>
+        <v>-1.7358</v>
       </c>
       <c r="L5" t="n">
-        <v>0.9953</v>
+        <v>4.1685</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2648</v>
+        <v>-0.333</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5803</v>
+        <v>-1.7003</v>
       </c>
       <c r="O5" t="n">
-        <v>0.845</v>
+        <v>1.3673</v>
       </c>
       <c r="P5" t="n">
-        <v>1.6676</v>
+        <v>0.3706</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.8529</v>
       </c>
       <c r="R5" t="n">
-        <v>1.6676</v>
+        <v>2.2234</v>
       </c>
       <c r="S5" t="n">
-        <v>1.7628</v>
+        <v>1.2084</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0074</v>
+        <v>0.2211</v>
       </c>
       <c r="U5" t="n">
-        <v>1.7703</v>
+        <v>0.9873</v>
       </c>
       <c r="V5" t="n">
-        <v>0.6294</v>
+        <v>1.2589</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9439</v>
+        <v>0.6289</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.3144</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. MEJIA BERIGUETE</t>
+          <t>A. DIAZ FERREIRA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>4.3134</v>
+        <v>4.829</v>
       </c>
       <c r="E6" t="n">
-        <v>2.743</v>
+        <v>2.1056</v>
       </c>
       <c r="F6" t="n">
-        <v>1.5703</v>
+        <v>2.7234</v>
       </c>
       <c r="G6" t="n">
-        <v>4.9903</v>
+        <v>1.7277</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5652</v>
+        <v>-0.1126</v>
       </c>
       <c r="I6" t="n">
-        <v>4.4251</v>
+        <v>1.8403</v>
       </c>
       <c r="J6" t="n">
-        <v>4.4355</v>
+        <v>1.463</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4636</v>
+        <v>0.4677</v>
       </c>
       <c r="L6" t="n">
-        <v>3.9718</v>
+        <v>0.9953</v>
       </c>
       <c r="M6" t="n">
-        <v>0.5548999999999999</v>
+        <v>0.2648</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1016</v>
+        <v>-0.5803</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4533</v>
+        <v>0.845</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1853</v>
+        <v>1.6676</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1117</v>
+        <v>1.6676</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.8623</v>
+        <v>0.8043</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.766</v>
+        <v>-0.3012</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0963</v>
+        <v>1.1055</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.6294</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.9439</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. OSÉS BERNALDÉZ</t>
+          <t>A. CUADRA CRESPO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.5103</v>
+        <v>3.1445</v>
       </c>
       <c r="E7" t="n">
-        <v>2.5103</v>
+        <v>2.1141</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1.0303</v>
       </c>
       <c r="G7" t="n">
-        <v>2.5103</v>
+        <v>2.9615</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6441</v>
+        <v>-0.8768</v>
       </c>
       <c r="I7" t="n">
-        <v>1.8662</v>
+        <v>3.8384</v>
       </c>
       <c r="J7" t="n">
-        <v>2.5103</v>
+        <v>3.4719</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6441</v>
+        <v>0.7857</v>
       </c>
       <c r="L7" t="n">
-        <v>1.8662</v>
+        <v>2.6862</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>-0.5104</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>-1.6626</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.1522</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>0.7411</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.6676</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>-0.8726</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>-0.7458</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>-0.1269</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.3144</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.3144</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. CUADRA CRESPO</t>
+          <t>P. OSÉS BERNALDÉZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.4567</v>
+        <v>2.5103</v>
       </c>
       <c r="E8" t="n">
-        <v>1.8203</v>
+        <v>2.5103</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6364</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>2.9615</v>
+        <v>2.5103</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.8768</v>
+        <v>0.6441</v>
       </c>
       <c r="I8" t="n">
-        <v>3.8384</v>
+        <v>1.8662</v>
       </c>
       <c r="J8" t="n">
-        <v>3.4719</v>
+        <v>2.5103</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7857</v>
+        <v>0.6441</v>
       </c>
       <c r="L8" t="n">
-        <v>2.6862</v>
+        <v>1.8662</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.5104</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.6626</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>1.1522</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>0.7411</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.6676</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.5604</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.0396</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5208</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>0.3144</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.3144</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>L. TOMPEA</t>
+          <t>L. MONES RIERA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5508</v>
+        <v>0.4531</v>
       </c>
       <c r="E11" t="n">
-        <v>1.3062</v>
+        <v>-0.1008</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.7554</v>
+        <v>0.5538999999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.7719</v>
+        <v>-2.4106</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.1375</v>
+        <v>-1.0881</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.6344</v>
+        <v>-1.3226</v>
       </c>
       <c r="J11" t="n">
-        <v>0.2778</v>
+        <v>-1.5609</v>
       </c>
       <c r="K11" t="n">
-        <v>0.7126</v>
+        <v>0.1074</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.4348</v>
+        <v>-1.6683</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.0497</v>
+        <v>-0.8497</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.8501</v>
+        <v>-1.1954</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1996</v>
+        <v>0.3457</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.1117</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9264</v>
+        <v>1.1117</v>
       </c>
       <c r="S11" t="n">
-        <v>1.9516</v>
+        <v>-0.1368</v>
       </c>
       <c r="T11" t="n">
-        <v>1.9549</v>
+        <v>-0.1131</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0032</v>
+        <v>-0.0236</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.6289</v>
+        <v>1.8888</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.5733</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.6289</v>
+        <v>0.3155</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>L. MONES RIERA</t>
+          <t>A. RODRIGUEZ LEIRO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4039</v>
+        <v>0.2438</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.1008</v>
+        <v>1.5083</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5047</v>
+        <v>-1.2644</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.4106</v>
+        <v>2.747</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.0881</v>
+        <v>2.0879</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.3226</v>
+        <v>0.659</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.5609</v>
+        <v>2.6307</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1074</v>
+        <v>2.3404</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.6683</v>
+        <v>0.2903</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.8497</v>
+        <v>0.1163</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.1954</v>
+        <v>-0.2524</v>
       </c>
       <c r="O12" t="n">
-        <v>0.3457</v>
+        <v>0.3687</v>
       </c>
       <c r="P12" t="n">
-        <v>1.1117</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R12" t="n">
-        <v>1.1117</v>
+        <v>0.9264</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.186</v>
+        <v>0.3295</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1131</v>
+        <v>0.434</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.07290000000000001</v>
+        <v>-0.1045</v>
       </c>
       <c r="V12" t="n">
-        <v>1.8888</v>
+        <v>-2.8327</v>
       </c>
       <c r="W12" t="n">
-        <v>1.5733</v>
+        <v>-0.63</v>
       </c>
       <c r="X12" t="n">
-        <v>0.3155</v>
+        <v>-2.2027</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. RODRIGUEZ LEIRO</t>
+          <t>I. VAZQUEZ FLORES</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.07149999999999999</v>
+        <v>0.2214</v>
       </c>
       <c r="E13" t="n">
-        <v>1.5083</v>
+        <v>0.7241</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.4368</v>
+        <v>-0.5028</v>
       </c>
       <c r="G13" t="n">
-        <v>2.747</v>
+        <v>-0.2584</v>
       </c>
       <c r="H13" t="n">
-        <v>2.0879</v>
+        <v>-0.4259</v>
       </c>
       <c r="I13" t="n">
-        <v>0.659</v>
+        <v>0.1675</v>
       </c>
       <c r="J13" t="n">
-        <v>2.6307</v>
+        <v>0.4694</v>
       </c>
       <c r="K13" t="n">
-        <v>2.3404</v>
+        <v>0.3865</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2903</v>
+        <v>0.0829</v>
       </c>
       <c r="M13" t="n">
-        <v>0.1163</v>
+        <v>-0.7278</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.2524</v>
+        <v>-0.8124</v>
       </c>
       <c r="O13" t="n">
-        <v>0.3687</v>
+        <v>0.08459999999999999</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="Q13" t="n">
         <v>-0.9264</v>
       </c>
       <c r="R13" t="n">
-        <v>0.9264</v>
+        <v>0.3706</v>
       </c>
       <c r="S13" t="n">
-        <v>0.1572</v>
+        <v>-0.2232</v>
       </c>
       <c r="T13" t="n">
-        <v>0.434</v>
+        <v>-0.07770000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2768</v>
+        <v>-0.1455</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.8327</v>
+        <v>1.2589</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.63</v>
+        <v>1.2589</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.2027</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>I. VAZQUEZ FLORES</t>
+          <t>L. TOMPEA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.1222</v>
+        <v>-0.5499000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>0.5283</v>
+        <v>0.0331</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.6505</v>
+        <v>-0.583</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.2584</v>
+        <v>-0.7719</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4259</v>
+        <v>-0.1375</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1675</v>
+        <v>-0.6344</v>
       </c>
       <c r="J14" t="n">
-        <v>0.4694</v>
+        <v>0.2778</v>
       </c>
       <c r="K14" t="n">
-        <v>0.3865</v>
+        <v>0.7126</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0829</v>
+        <v>-0.4348</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.7278</v>
+        <v>-1.0497</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.8124</v>
+        <v>-0.8501</v>
       </c>
       <c r="O14" t="n">
-        <v>0.08459999999999999</v>
+        <v>-0.1996</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.5558999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>-0.9264</v>
       </c>
       <c r="R14" t="n">
-        <v>0.3706</v>
+        <v>0.9264</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.5668</v>
+        <v>0.8509</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2736</v>
+        <v>0.6818</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2932</v>
+        <v>0.1691</v>
       </c>
       <c r="V14" t="n">
-        <v>1.2589</v>
+        <v>-0.6289</v>
       </c>
       <c r="W14" t="n">
-        <v>1.2589</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-0.6289</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-5.1076</v>
+        <v>-5.1568</v>
       </c>
       <c r="E15" t="n">
         <v>-6.0904</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9828</v>
+        <v>0.9336</v>
       </c>
       <c r="G15" t="n">
         <v>-4.8895</v>
@@ -1624,13 +1624,13 @@
         <v>1.6676</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.0328</v>
+        <v>-0.08210000000000001</v>
       </c>
       <c r="T15" t="n">
         <v>-0.4414</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4086</v>
+        <v>0.3594</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>34.12440000000001</v>
+        <v>34.1242</v>
       </c>
       <c r="E16" t="n">
-        <v>19.9473</v>
+        <v>19.9472</v>
       </c>
       <c r="F16" t="n">
-        <v>14.177</v>
+        <v>14.1769</v>
       </c>
       <c r="G16" t="n">
         <v>22.0091</v>
@@ -1672,7 +1672,7 @@
         <v>-6.2529</v>
       </c>
       <c r="I16" t="n">
-        <v>28.262</v>
+        <v>28.26199999999999</v>
       </c>
       <c r="J16" t="n">
         <v>24.049</v>
@@ -1687,13 +1687,13 @@
         <v>-2.0397</v>
       </c>
       <c r="N16" t="n">
-        <v>-9.298999999999999</v>
+        <v>-9.299000000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>7.2594</v>
+        <v>7.259399999999999</v>
       </c>
       <c r="P16" t="n">
-        <v>5.558599999999999</v>
+        <v>5.5586</v>
       </c>
       <c r="Q16" t="n">
         <v>-9.264200000000001</v>
@@ -1702,16 +1702,16 @@
         <v>14.8229</v>
       </c>
       <c r="S16" t="n">
-        <v>2.779300000000001</v>
+        <v>2.7794</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.8141999999999999</v>
+        <v>-0.8142000000000003</v>
       </c>
       <c r="U16" t="n">
-        <v>3.593699999999999</v>
+        <v>3.5936</v>
       </c>
       <c r="V16" t="n">
-        <v>3.7771</v>
+        <v>3.777099999999999</v>
       </c>
       <c r="W16" t="n">
         <v>5.977099999999999</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R. HENRIQUE RIBEIRO FORMOSO</t>
+          <t>Á. LLAMAS JIMENEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.0261</v>
+        <v>1.2662</v>
       </c>
       <c r="E17" t="n">
-        <v>1.8186</v>
+        <v>1.2662</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2075</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.2131</v>
+        <v>1.2662</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1857</v>
+        <v>0.6441</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.0274</v>
+        <v>0.6221</v>
       </c>
       <c r="J17" t="n">
-        <v>0.7116</v>
+        <v>1.2662</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.0349</v>
+        <v>0.6441</v>
       </c>
       <c r="L17" t="n">
-        <v>0.7465000000000001</v>
+        <v>0.6221</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.9247</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1508</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.7738</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.5558999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.0382</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.4823</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.2212</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>1.5719</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6494</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.5738</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.5733</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0.0005</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Á. LLAMAS JIMENEZ</t>
+          <t>R. HENRIQUE RIBEIRO FORMOSO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.2662</v>
+        <v>0.6546</v>
       </c>
       <c r="E18" t="n">
-        <v>1.2662</v>
+        <v>0.5455</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>0.109</v>
       </c>
       <c r="G18" t="n">
-        <v>1.2662</v>
+        <v>-1.2131</v>
       </c>
       <c r="H18" t="n">
-        <v>0.6441</v>
+        <v>-0.1857</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6221</v>
+        <v>-1.0274</v>
       </c>
       <c r="J18" t="n">
-        <v>1.2662</v>
+        <v>0.7116</v>
       </c>
       <c r="K18" t="n">
-        <v>0.6441</v>
+        <v>-0.0349</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6221</v>
+        <v>0.7465000000000001</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>-1.9247</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>-0.1508</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>-1.7738</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-2.0382</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.4823</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>0.8496</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>0.2988</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>0.5508999999999999</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.5738</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.5733</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>0.0005</v>
       </c>
     </row>
     <row r="19">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.5149</v>
+        <v>-0.8529</v>
       </c>
       <c r="E20" t="n">
-        <v>0.4516</v>
+        <v>0.9412</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.9665</v>
+        <v>-1.7941</v>
       </c>
       <c r="G20" t="n">
         <v>-1.4868</v>
@@ -2014,13 +2014,13 @@
         <v>1.1117</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.1398</v>
+        <v>-0.4778</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6019</v>
+        <v>-0.1122</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.538</v>
+        <v>-0.3656</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>O. KANTE</t>
+          <t>A. VEGUILLA SANCHEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.8063</v>
+        <v>-2.7061</v>
       </c>
       <c r="E21" t="n">
-        <v>0.3253</v>
+        <v>-0.9963</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.1316</v>
+        <v>-1.7098</v>
       </c>
       <c r="G21" t="n">
-        <v>0.4642</v>
+        <v>-1.0856</v>
       </c>
       <c r="H21" t="n">
-        <v>2.9985</v>
+        <v>0.9297</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.5343</v>
+        <v>-2.0153</v>
       </c>
       <c r="J21" t="n">
-        <v>4.5838</v>
+        <v>0.601</v>
       </c>
       <c r="K21" t="n">
-        <v>3.2247</v>
+        <v>0.5583</v>
       </c>
       <c r="L21" t="n">
-        <v>1.3591</v>
+        <v>0.0427</v>
       </c>
       <c r="M21" t="n">
-        <v>-4.1197</v>
+        <v>-1.6865</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2263</v>
+        <v>0.3715</v>
       </c>
       <c r="O21" t="n">
-        <v>-3.8934</v>
+        <v>-2.058</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.7793</v>
+        <v>-0.3706</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.891</v>
+        <v>-0.9264</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1117</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="S21" t="n">
-        <v>1.4532</v>
+        <v>-0.6211</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2624</v>
+        <v>-0.6709000000000001</v>
       </c>
       <c r="U21" t="n">
-        <v>1.1908</v>
+        <v>0.0497</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.9444</v>
+        <v>-0.6289</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.63</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.3144</v>
+        <v>-0.6289</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. VEGUILLA SANCHEZ</t>
+          <t>J. VAZQUEZ SUAREZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.7862</v>
+        <v>-3.2796</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.5839</v>
+        <v>-1.8643</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.2023</v>
+        <v>-1.4153</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.0856</v>
+        <v>-2.9562</v>
       </c>
       <c r="H22" t="n">
-        <v>0.9297</v>
+        <v>0.7208</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.0153</v>
+        <v>-3.677</v>
       </c>
       <c r="J22" t="n">
-        <v>0.601</v>
+        <v>-0.3184</v>
       </c>
       <c r="K22" t="n">
-        <v>0.5583</v>
+        <v>0.8629</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0427</v>
+        <v>-1.1813</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.6865</v>
+        <v>-2.6378</v>
       </c>
       <c r="N22" t="n">
-        <v>0.3715</v>
+        <v>-0.1421</v>
       </c>
       <c r="O22" t="n">
-        <v>-2.058</v>
+        <v>-2.4957</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.3706</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9264</v>
+        <v>-1.1117</v>
       </c>
       <c r="R22" t="n">
-        <v>0.5558999999999999</v>
+        <v>1.6676</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.7012</v>
+        <v>-0.8792</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.2584</v>
+        <v>-0.7486</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4427</v>
+        <v>-0.1306</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.6289</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.3144</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.6289</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. VAZQUEZ SUAREZ</t>
+          <t>J. BRAVO ORTEGA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.9399</v>
+        <v>-3.4729</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.6477</v>
+        <v>-3.639</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.2922</v>
+        <v>0.1661</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.9562</v>
+        <v>-2.8205</v>
       </c>
       <c r="H23" t="n">
-        <v>0.7208</v>
+        <v>0.9505</v>
       </c>
       <c r="I23" t="n">
-        <v>-3.677</v>
+        <v>-3.771</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.3184</v>
+        <v>-1.8089</v>
       </c>
       <c r="K23" t="n">
-        <v>0.8629</v>
+        <v>1.4554</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.1813</v>
+        <v>-3.2643</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.6378</v>
+        <v>-1.0115</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.1421</v>
+        <v>-0.5048</v>
       </c>
       <c r="O23" t="n">
-        <v>-2.4957</v>
+        <v>-0.5067</v>
       </c>
       <c r="P23" t="n">
-        <v>0.5558999999999999</v>
+        <v>-2.0382</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.1117</v>
+        <v>-2.9646</v>
       </c>
       <c r="R23" t="n">
-        <v>1.6676</v>
+        <v>0.9264</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.5395</v>
+        <v>0.1275</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.532</v>
+        <v>-0.1237</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0075</v>
+        <v>0.2512</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.2583</v>
       </c>
       <c r="W23" t="n">
-        <v>0.3144</v>
+        <v>1.2583</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.3144</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. BRAVO ORTEGA</t>
+          <t>O. KANTE</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.2821</v>
+        <v>-3.4756</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.2265</v>
+        <v>-0.5561</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.0555</v>
+        <v>-2.9195</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.8205</v>
+        <v>0.4642</v>
       </c>
       <c r="H24" t="n">
-        <v>0.9505</v>
+        <v>2.9985</v>
       </c>
       <c r="I24" t="n">
-        <v>-3.771</v>
+        <v>-2.5343</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.8089</v>
+        <v>4.5838</v>
       </c>
       <c r="K24" t="n">
-        <v>1.4554</v>
+        <v>3.2247</v>
       </c>
       <c r="L24" t="n">
-        <v>-3.2643</v>
+        <v>1.3591</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.0115</v>
+        <v>-4.1197</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.5048</v>
+        <v>-0.2263</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.5067</v>
+        <v>-3.8934</v>
       </c>
       <c r="P24" t="n">
-        <v>-2.0382</v>
+        <v>-2.7793</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.9646</v>
+        <v>-3.891</v>
       </c>
       <c r="R24" t="n">
-        <v>0.9264</v>
+        <v>1.1117</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.6817</v>
+        <v>-0.2161</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.7113</v>
+        <v>-0.6189</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0296</v>
+        <v>0.4029</v>
       </c>
       <c r="V24" t="n">
-        <v>1.2583</v>
+        <v>-0.9444</v>
       </c>
       <c r="W24" t="n">
-        <v>1.2583</v>
+        <v>-0.63</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="25">
@@ -2359,10 +2359,10 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.5897</v>
+        <v>-5.9814</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.2517</v>
+        <v>-1.6435</v>
       </c>
       <c r="F25" t="n">
         <v>-4.3379</v>
@@ -2404,10 +2404,10 @@
         <v>1.1117</v>
       </c>
       <c r="S25" t="n">
-        <v>0.7287</v>
+        <v>0.337</v>
       </c>
       <c r="T25" t="n">
-        <v>0.4303</v>
+        <v>0.0386</v>
       </c>
       <c r="U25" t="n">
         <v>0.2984</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-6.6511</v>
+        <v>-6.4799</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.483</v>
+        <v>-2.2872</v>
       </c>
       <c r="F26" t="n">
-        <v>-4.1681</v>
+        <v>-4.1927</v>
       </c>
       <c r="G26" t="n">
         <v>-3.745</v>
@@ -2482,13 +2482,13 @@
         <v>0.1853</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.8881</v>
+        <v>-0.7169</v>
       </c>
       <c r="T26" t="n">
-        <v>-1.0396</v>
+        <v>-0.8437</v>
       </c>
       <c r="U26" t="n">
-        <v>0.1514</v>
+        <v>0.1268</v>
       </c>
       <c r="V26" t="n">
         <v>-2.2033</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-10.1685</v>
+        <v>-10.1187</v>
       </c>
       <c r="E27" t="n">
-        <v>-6.1677</v>
+        <v>-6.2657</v>
       </c>
       <c r="F27" t="n">
-        <v>-4.0008</v>
+        <v>-3.853</v>
       </c>
       <c r="G27" t="n">
         <v>-6.1391</v>
@@ -2560,13 +2560,13 @@
         <v>1.1117</v>
       </c>
       <c r="S27" t="n">
-        <v>-1.2321</v>
+        <v>-1.1823</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.715</v>
+        <v>-0.8129</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.5171</v>
+        <v>-0.3694</v>
       </c>
       <c r="V27" t="n">
         <v>-0.9444</v>
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-34.1243</v>
+        <v>-34.1242</v>
       </c>
       <c r="E28" t="n">
-        <v>-14.1767</v>
+        <v>-14.1771</v>
       </c>
       <c r="F28" t="n">
-        <v>-19.9474</v>
+        <v>-19.9472</v>
       </c>
       <c r="G28" t="n">
         <v>-22.0092</v>
@@ -2614,7 +2614,7 @@
         <v>2.0398</v>
       </c>
       <c r="K28" t="n">
-        <v>9.299300000000002</v>
+        <v>9.299299999999999</v>
       </c>
       <c r="L28" t="n">
         <v>-7.2594</v>
@@ -2641,10 +2641,10 @@
         <v>-2.7793</v>
       </c>
       <c r="T28" t="n">
-        <v>-3.5936</v>
+        <v>-3.5935</v>
       </c>
       <c r="U28" t="n">
-        <v>0.8143000000000001</v>
+        <v>0.8143</v>
       </c>
       <c r="V28" t="n">
         <v>-3.7772</v>
